--- a/arm_torque_budget_and_timeline.xlsx
+++ b/arm_torque_budget_and_timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erico\Documents\GitHub\6-DOF-Arm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD60D5E-8F4D-4EDB-B4F8-B854BFCBB44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6229C372-2A3E-41CF-8D58-A146414E86EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="14856" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Torque Budget" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="189">
   <si>
     <t>6-DoF Arm — Gravity Torque Budget v2 (elbow-mounted forearm roll)</t>
   </si>
@@ -593,6 +593,18 @@
   </si>
   <si>
     <t>Price per Unit</t>
+  </si>
+  <si>
+    <t>Ordered On</t>
+  </si>
+  <si>
+    <t>(only ordered 1)</t>
+  </si>
+  <si>
+    <t>shipping 11.07</t>
+  </si>
+  <si>
+    <t>shipping 30</t>
   </si>
 </sst>
 </file>
@@ -722,7 +734,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -760,13 +772,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -856,6 +879,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1150,9 +1177,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="45.88671875" customWidth="1"/>
+    <col min="1" max="1" width="45.86328125" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -1162,17 +1189,17 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="42" t="s">
         <v>2</v>
       </c>
@@ -1185,7 +1212,7 @@
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1196,7 +1223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1207,7 +1234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1221,7 +1248,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1235,7 +1262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -1250,7 +1277,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A11" s="42" t="s">
         <v>12</v>
       </c>
@@ -1263,7 +1290,7 @@
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -1277,7 +1304,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -1291,7 +1318,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -1305,7 +1332,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -1319,7 +1346,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -1333,7 +1360,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -1344,7 +1371,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -1358,7 +1385,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A20" s="42" t="s">
         <v>27</v>
       </c>
@@ -1371,7 +1398,7 @@
       <c r="H20" s="42"/>
       <c r="I20" s="42"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
@@ -1382,7 +1409,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A22" s="3" t="s">
         <v>30</v>
       </c>
@@ -1393,7 +1420,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A24" s="42" t="s">
         <v>32</v>
       </c>
@@ -1406,7 +1433,7 @@
       <c r="H24" s="42"/>
       <c r="I24" s="42"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
@@ -1420,7 +1447,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
@@ -1434,7 +1461,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -1448,7 +1475,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
@@ -1462,7 +1489,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -1476,7 +1503,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A30" s="3" t="s">
         <v>47</v>
       </c>
@@ -1490,7 +1517,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
@@ -1504,7 +1531,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
@@ -1518,7 +1545,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
@@ -1532,7 +1559,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
@@ -1543,7 +1570,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A36" s="42" t="s">
         <v>56</v>
       </c>
@@ -1556,7 +1583,7 @@
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
     </row>
-    <row r="37" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
@@ -1577,7 +1604,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A38" s="13" t="s">
         <v>63</v>
       </c>
@@ -1600,7 +1627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A39" s="13" t="s">
         <v>65</v>
       </c>
@@ -1623,7 +1650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A40" s="13" t="s">
         <v>66</v>
       </c>
@@ -1648,7 +1675,7 @@
         <v>3.5316E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A41" s="13" t="s">
         <v>67</v>
       </c>
@@ -1673,7 +1700,7 @@
         <v>4.7088000000000005E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A42" s="13" t="s">
         <v>68</v>
       </c>
@@ -1698,7 +1725,7 @@
         <v>0.34531200000000006</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A43" s="13" t="s">
         <v>69</v>
       </c>
@@ -1723,7 +1750,7 @@
         <v>0.29430000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A44" s="13" t="s">
         <v>70</v>
       </c>
@@ -1748,7 +1775,7 @@
         <v>0.47088000000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A45" s="17" t="s">
         <v>71</v>
       </c>
@@ -1764,7 +1791,7 @@
         <v>1.1928960000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A47" s="42" t="s">
         <v>72</v>
       </c>
@@ -1777,7 +1804,7 @@
       <c r="H47" s="42"/>
       <c r="I47" s="42"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
@@ -1786,7 +1813,7 @@
         <v>5.8860000000000003E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
@@ -1795,7 +1822,7 @@
         <v>0.15696000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A50" s="21" t="s">
         <v>75</v>
       </c>
@@ -1807,7 +1834,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A52" s="42" t="s">
         <v>77</v>
       </c>
@@ -1820,7 +1847,7 @@
       <c r="H52" s="42"/>
       <c r="I52" s="42"/>
     </row>
-    <row r="53" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A53" s="12" t="s">
         <v>78</v>
       </c>
@@ -1849,7 +1876,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A54" s="13" t="s">
         <v>87</v>
       </c>
@@ -1885,7 +1912,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A55" s="13" t="s">
         <v>88</v>
       </c>
@@ -1922,7 +1949,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" s="13" t="s">
         <v>89</v>
       </c>
@@ -1959,7 +1986,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" s="13" t="s">
         <v>90</v>
       </c>
@@ -1992,7 +2019,7 @@
       </c>
       <c r="I57" s="13"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" s="13" t="s">
         <v>91</v>
       </c>
@@ -2025,7 +2052,7 @@
       </c>
       <c r="I58" s="13"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" s="13" t="s">
         <v>92</v>
       </c>
@@ -2057,37 +2084,37 @@
       </c>
       <c r="I59" s="13"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A61" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>99</v>
       </c>
@@ -2121,19 +2148,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C3DC63-880C-4C7A-BD99-15B2870A7881}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.86328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" customWidth="1"/>
-    <col min="10" max="10" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1328125" customWidth="1"/>
+    <col min="8" max="8" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A1" s="31" t="s">
         <v>102</v>
       </c>
@@ -2155,8 +2183,11 @@
       <c r="G1" s="31" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H1" s="43" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -2179,7 +2210,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A3" s="38">
         <v>2</v>
       </c>
@@ -2190,7 +2221,7 @@
         <v>173</v>
       </c>
       <c r="D3" s="38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="39">
         <v>29</v>
@@ -2201,8 +2232,17 @@
       <c r="G3" s="40" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H3" s="44">
+        <v>46213</v>
+      </c>
+      <c r="I3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -2225,7 +2265,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A5" s="38">
         <v>4</v>
       </c>
@@ -2248,7 +2288,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -2270,8 +2310,11 @@
       <c r="G6" s="37" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H6" s="44">
+        <v>46213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A7" s="38"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
@@ -2280,7 +2323,7 @@
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A8" s="35">
         <v>6</v>
       </c>
@@ -2302,8 +2345,14 @@
       <c r="G8" s="37" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="H8" s="44">
+        <v>46213</v>
+      </c>
+      <c r="K8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A9" s="41"/>
       <c r="B9" s="33"/>
       <c r="C9" s="33"/>
@@ -2312,16 +2361,16 @@
       <c r="F9" s="33"/>
       <c r="G9" s="33"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
       <c r="F10" s="32" t="s">
         <v>181</v>
       </c>
       <c r="G10" s="34">
         <f>SUMPRODUCT($D$2:$D$8,$E$2:$E$8)</f>
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
       <c r="N13" t="s">
         <v>183</v>
       </c>
@@ -2342,7 +2391,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2352,17 +2401,17 @@
     <col min="6" max="6" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="16.899999999999999" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="27" t="s">
         <v>102</v>
       </c>
@@ -2382,7 +2431,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A5" s="28" t="s">
         <v>108</v>
       </c>
@@ -2402,7 +2451,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.45">
       <c r="A6" s="28" t="s">
         <v>114</v>
       </c>
@@ -2422,7 +2471,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A7" s="28" t="s">
         <v>120</v>
       </c>
@@ -2442,7 +2491,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A8" s="28" t="s">
         <v>126</v>
       </c>
@@ -2462,7 +2511,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.45">
       <c r="A9" s="28" t="s">
         <v>132</v>
       </c>
@@ -2482,7 +2531,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A10" s="28" t="s">
         <v>138</v>
       </c>
@@ -2502,7 +2551,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A11" s="28" t="s">
         <v>144</v>
       </c>
@@ -2522,7 +2571,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="52.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.45">
       <c r="A12" s="28" t="s">
         <v>150</v>
       </c>
@@ -2542,7 +2591,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
       <c r="A13" s="28" t="s">
         <v>156</v>
       </c>
@@ -2562,7 +2611,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.45">
       <c r="A14" s="28" t="s">
         <v>162</v>
       </c>

--- a/arm_torque_budget_and_timeline.xlsx
+++ b/arm_torque_budget_and_timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ethan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erico\Documents\GitHub\6-DOF-Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6229C372-2A3E-41CF-8D58-A146414E86EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C965C7F3-69B8-4E7C-AD35-2E193063853D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Torque Budget" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="190">
   <si>
     <t>6-DoF Arm — Gravity Torque Budget v2 (elbow-mounted forearm roll)</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>shipping 30</t>
+  </si>
+  <si>
+    <t># Ordered</t>
   </si>
 </sst>
 </file>
@@ -789,7 +792,7 @@
     <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -855,34 +858,41 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1177,9 +1187,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I67"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.86328125" customWidth="1"/>
+    <col min="1" max="1" width="45.85546875" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
@@ -1189,30 +1199,30 @@
     <col min="9" max="9" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:9" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" s="42" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -1223,7 +1233,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -1234,7 +1244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -1248,7 +1258,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -1262,7 +1272,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>10</v>
       </c>
@@ -1277,20 +1287,20 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A11" s="42" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -1304,7 +1314,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>16</v>
       </c>
@@ -1318,7 +1328,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
@@ -1332,7 +1342,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -1346,7 +1356,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>22</v>
       </c>
@@ -1360,7 +1370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
@@ -1371,7 +1381,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
@@ -1385,20 +1395,20 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A20" s="42" t="s">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B20" s="36"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
@@ -1409,7 +1419,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>30</v>
       </c>
@@ -1420,20 +1430,20 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A24" s="42" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
         <v>32</v>
       </c>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B24" s="36"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="36"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
@@ -1447,7 +1457,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>36</v>
       </c>
@@ -1461,7 +1471,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -1475,7 +1485,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>41</v>
       </c>
@@ -1489,7 +1499,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>44</v>
       </c>
@@ -1503,7 +1513,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>47</v>
       </c>
@@ -1517,7 +1527,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>49</v>
       </c>
@@ -1531,7 +1541,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>51</v>
       </c>
@@ -1545,7 +1555,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>53</v>
       </c>
@@ -1559,7 +1569,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>55</v>
       </c>
@@ -1570,20 +1580,20 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A36" s="42" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="B36" s="42"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-    </row>
-    <row r="37" spans="1:9" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="B36" s="36"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+    </row>
+    <row r="37" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="12" t="s">
         <v>57</v>
       </c>
@@ -1604,7 +1614,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>63</v>
       </c>
@@ -1627,7 +1637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>65</v>
       </c>
@@ -1650,7 +1660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>66</v>
       </c>
@@ -1675,7 +1685,7 @@
         <v>3.5316E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>67</v>
       </c>
@@ -1700,7 +1710,7 @@
         <v>4.7088000000000005E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>68</v>
       </c>
@@ -1725,7 +1735,7 @@
         <v>0.34531200000000006</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>69</v>
       </c>
@@ -1750,7 +1760,7 @@
         <v>0.29430000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>70</v>
       </c>
@@ -1775,7 +1785,7 @@
         <v>0.47088000000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>71</v>
       </c>
@@ -1791,20 +1801,20 @@
         <v>1.1928960000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A47" s="42" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B47" s="42"/>
-      <c r="C47" s="42"/>
-      <c r="D47" s="42"/>
-      <c r="E47" s="42"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="42"/>
-      <c r="H47" s="42"/>
-      <c r="I47" s="42"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="B47" s="36"/>
+      <c r="C47" s="36"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>73</v>
       </c>
@@ -1813,7 +1823,7 @@
         <v>5.8860000000000003E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>74</v>
       </c>
@@ -1822,7 +1832,7 @@
         <v>0.15696000000000002</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>75</v>
       </c>
@@ -1834,20 +1844,20 @@
         <v>76</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A52" s="42" t="s">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="B52" s="42"/>
-      <c r="C52" s="42"/>
-      <c r="D52" s="42"/>
-      <c r="E52" s="42"/>
-      <c r="F52" s="42"/>
-      <c r="G52" s="42"/>
-      <c r="H52" s="42"/>
-      <c r="I52" s="42"/>
-    </row>
-    <row r="53" spans="1:9" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="B52" s="36"/>
+      <c r="C52" s="36"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+    </row>
+    <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="12" t="s">
         <v>78</v>
       </c>
@@ -1876,7 +1886,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="13" t="s">
         <v>87</v>
       </c>
@@ -1912,7 +1922,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>88</v>
       </c>
@@ -1949,7 +1959,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="13" t="s">
         <v>89</v>
       </c>
@@ -1986,7 +1996,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>90</v>
       </c>
@@ -2019,7 +2029,7 @@
       </c>
       <c r="I57" s="13"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="13" t="s">
         <v>91</v>
       </c>
@@ -2052,7 +2062,7 @@
       </c>
       <c r="I58" s="13"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>92</v>
       </c>
@@ -2084,37 +2094,37 @@
       </c>
       <c r="I59" s="13"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>99</v>
       </c>
@@ -2148,20 +2158,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C3DC63-880C-4C7A-BD99-15B2870A7881}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.86328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.1328125" customWidth="1"/>
-    <col min="8" max="8" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="31" t="s">
         <v>102</v>
       </c>
@@ -2183,194 +2195,225 @@
       <c r="G1" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="35" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" s="35">
+      <c r="I1" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="38">
         <v>1</v>
       </c>
-      <c r="B2" s="35">
+      <c r="B2" s="38">
         <v>3</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="38">
         <v>3</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="39">
         <v>69</v>
       </c>
-      <c r="F2" s="35" t="s">
+      <c r="F2" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="40" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A3" s="38">
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="41">
         <v>2</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="41">
         <v>3</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="38">
+      <c r="D3" s="41">
         <v>3</v>
       </c>
-      <c r="E3" s="39">
+      <c r="E3" s="42">
         <v>29</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="43" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="44">
+      <c r="H3" s="45">
         <v>46213</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="K3" t="s">
+      <c r="J3" s="37"/>
+      <c r="K3" s="37" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A4" s="35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="38">
         <v>3</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="38">
         <v>3</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="38">
         <v>2</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="39">
         <v>94</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="40" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A5" s="38">
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="37"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="41">
         <v>4</v>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="41">
         <v>3</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="38">
+      <c r="D5" s="41">
         <v>2</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="42">
         <v>74</v>
       </c>
-      <c r="F5" s="38" t="s">
+      <c r="F5" s="41" t="s">
         <v>182</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="43" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A6" s="35">
+      <c r="H5" s="34"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="38">
         <v>5</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="38">
         <v>3</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="38">
         <v>1</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="39">
         <v>219</v>
       </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="38" t="s">
         <v>182</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="46">
         <v>46213</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="38"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="35">
+      <c r="I6" s="46"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="44"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="38">
         <v>6</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="38">
         <v>3</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="38">
         <v>3</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="39">
         <v>65</v>
       </c>
-      <c r="F8" s="35" t="s">
+      <c r="F8" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="46">
         <v>46213</v>
       </c>
-      <c r="K8" t="s">
+      <c r="I8" s="46"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A9" s="41"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="34"/>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="44"/>
+      <c r="H9" s="44"/>
+      <c r="I9" s="44"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F10" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="33">
         <f>SUMPRODUCT($D$2:$D$8,$E$2:$E$8)</f>
         <v>1044</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="N13" t="s">
         <v>183</v>
       </c>
@@ -2391,7 +2434,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -2401,17 +2444,17 @@
     <col min="6" max="6" width="56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.899999999999999" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="27" t="s">
         <v>102</v>
       </c>
@@ -2431,7 +2474,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="28" t="s">
         <v>108</v>
       </c>
@@ -2451,7 +2494,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A6" s="28" t="s">
         <v>114</v>
       </c>
@@ -2471,7 +2514,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="28" t="s">
         <v>120</v>
       </c>
@@ -2491,7 +2534,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>126</v>
       </c>
@@ -2511,7 +2554,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="51" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A9" s="28" t="s">
         <v>132</v>
       </c>
@@ -2531,7 +2574,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A10" s="28" t="s">
         <v>138</v>
       </c>
@@ -2551,7 +2594,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A11" s="28" t="s">
         <v>144</v>
       </c>
@@ -2571,7 +2614,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="28" t="s">
         <v>150</v>
       </c>
@@ -2591,7 +2634,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A13" s="28" t="s">
         <v>156</v>
       </c>
@@ -2611,7 +2654,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="28" t="s">
         <v>162</v>
       </c>

--- a/arm_torque_budget_and_timeline.xlsx
+++ b/arm_torque_budget_and_timeline.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\erico\Documents\GitHub\6-DOF-Arm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C965C7F3-69B8-4E7C-AD35-2E193063853D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E648546-19A6-497C-9520-6A3132575421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Torque Budget" sheetId="1" r:id="rId1"/>
-    <sheet name="BOM" sheetId="3" r:id="rId2"/>
-    <sheet name="Timeline" sheetId="2" r:id="rId3"/>
+    <sheet name="Timeline" sheetId="2" r:id="rId2"/>
+    <sheet name="BOM" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -2156,6 +2156,255 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="6" max="6" width="56" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" s="27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="E6" s="30" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="30" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>136</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="30" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>145</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="F11" s="30" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>153</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>154</v>
+      </c>
+      <c r="F12" s="30" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13" s="30" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="30" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>165</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C3DC63-880C-4C7A-BD99-15B2870A7881}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2429,253 +2678,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="52" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="56" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>103</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A5" s="28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="C5" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="30" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="30" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
-        <v>120</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="30" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="28" t="s">
-        <v>132</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>133</v>
-      </c>
-      <c r="C9" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" s="30" t="s">
-        <v>136</v>
-      </c>
-      <c r="F9" s="30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E10" s="30" t="s">
-        <v>142</v>
-      </c>
-      <c r="F10" s="30" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>147</v>
-      </c>
-      <c r="E11" s="30" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="30" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="51" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>153</v>
-      </c>
-      <c r="E12" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="F12" s="30" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>159</v>
-      </c>
-      <c r="E13" s="30" t="s">
-        <v>160</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>165</v>
-      </c>
-      <c r="E14" s="30" t="s">
-        <v>166</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>167</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
 </file>